--- a/processed_ruby_restored_xlsx/sc012_１日目後半.ss.xlsx
+++ b/processed_ruby_restored_xlsx/sc012_１日目後半.ss.xlsx
@@ -872,7 +872,7 @@
       </c>
       <c r="B27" s="1" t="inlineStr">
         <is>
-          <t>「I-is that so？」</t>
+          <t>I-is that so？</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -1363,7 +1363,7 @@
       <c r="B59" s="1" t="inlineStr">
         <is>
           <t>「But asking someone to give me a ride when it's not
-for a class...」</t>
+for a class..."</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="B60" s="1" t="inlineStr">
         <is>
-          <t>Hey…'</t>
+          <t>Hey…」</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -2369,8 +2369,8 @@
       </c>
       <c r="B125" s="1" t="inlineStr">
         <is>
-          <t>And for some reason, her voice went up and she was
-all flustered.</t>
+          <t>And for some reason, their voice went up and they
+were all flustered.</t>
         </is>
       </c>
       <c r="C125" t="n">
@@ -6336,7 +6336,7 @@
       </c>
       <c r="B383" s="1" t="inlineStr">
         <is>
-          <t>Miruku</t>
+          <t>Miru</t>
         </is>
       </c>
       <c r="C383" t="n">
@@ -7357,7 +7357,7 @@
       </c>
       <c r="B450" s="1" t="inlineStr">
         <is>
-          <t>「Hoho~...！」</t>
+          <t>Hoho~...！</t>
         </is>
       </c>
       <c r="C450" t="n">
@@ -7403,8 +7403,8 @@
       </c>
       <c r="B453" s="1" t="inlineStr">
         <is>
-          <t>「Miru-chan, you might end up drawing your own order
-too, you know？」</t>
+          <t>「Miru-chan, orders can be withdrawn by she herself,
+you know？」</t>
         </is>
       </c>
       <c r="C453" t="n">
@@ -7420,7 +7420,7 @@
       <c r="B454" s="1" t="inlineStr">
         <is>
           <t>But since I can't say anything and it pisses me off,
-I give her a light little threat.</t>
+I give them a light little threat.</t>
         </is>
       </c>
       <c r="C454" t="n">
@@ -7663,7 +7663,7 @@
       </c>
       <c r="B470" s="1" t="inlineStr">
         <is>
-          <t>「Ah... R-Rin...！」</t>
+          <t>Ah... R-Rin...！</t>
         </is>
       </c>
       <c r="C470" t="n">
@@ -7693,8 +7693,8 @@
       </c>
       <c r="B472" s="1" t="inlineStr">
         <is>
-          <t>「F-fufu... If you're gonna blame anyone, blame
-yourself—」</t>
+          <t>F-fufu... If you're gonna blame anyone, blame
+herself—</t>
         </is>
       </c>
       <c r="C472" t="n">
@@ -7724,7 +7724,7 @@
       </c>
       <c r="B474" s="1" t="inlineStr">
         <is>
-          <t>「Hey！ Rin, w-wait... whoa！？」</t>
+          <t>Hey！ Rin, w-wait... whoa！？</t>
         </is>
       </c>
       <c r="C474" t="n">
@@ -7785,7 +7785,7 @@
       </c>
       <c r="B478" s="1" t="inlineStr">
         <is>
-          <t>「Puwaah！　...Uuuu...！」</t>
+          <t>Puwaah！　...Uuuu...！</t>
         </is>
       </c>
       <c r="C478" t="n">
@@ -9269,7 +9269,7 @@
       <c r="B575" s="1" t="inlineStr">
         <is>
           <t>Sheesh... if she does a handstand in her usual
-clothes, h-her panties would be totally visible...</t>
+clothes, m-my panties would be totally visible...</t>
         </is>
       </c>
       <c r="C575" t="n">
@@ -10389,7 +10389,7 @@
       </c>
       <c r="B648" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo-chan joined Nono-chan in applauding.</t>
+          <t>Rurichiyo-chan joined Monono-chan in applauding.</t>
         </is>
       </c>
       <c r="C648" t="n">
@@ -11203,8 +11203,9 @@
       </c>
       <c r="B701" s="1" t="inlineStr">
         <is>
-          <t>She tears it into bite-sized pieces, bring one to her
-mouth, and her face just lights up with happiness.</t>
+          <t>They tear it into bite-sized pieces, bring one to
+their mouth, and their face just lights up with
+happiness.</t>
         </is>
       </c>
       <c r="C701" t="n">
@@ -11783,7 +11784,7 @@
       </c>
       <c r="B739" s="1" t="inlineStr">
         <is>
-          <t>「Alright, next up is Janitor-sensei, right！」</t>
+          <t>Alright, next up is Janitor-sensei, right！</t>
         </is>
       </c>
       <c r="C739" t="n">
@@ -13633,7 +13634,7 @@
       </c>
       <c r="B860" s="1" t="inlineStr">
         <is>
-          <t>And just as she expected, I pat her head.</t>
+          <t>And just as she expected, he pats her head.</t>
         </is>
       </c>
       <c r="C860" t="n">
@@ -13739,7 +13740,7 @@
       </c>
       <c r="B867" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo</t>
+          <t>Ruri</t>
         </is>
       </c>
       <c r="C867" t="n">
@@ -14275,7 +14276,7 @@
       </c>
       <c r="B902" s="1" t="inlineStr">
         <is>
-          <t>「I'm definitely thinking naughty things.」</t>
+          <t>「He's definitely thinking naughty things.」</t>
         </is>
       </c>
       <c r="C902" t="n">
@@ -15532,7 +15533,7 @@
       </c>
       <c r="B984" s="1" t="inlineStr">
         <is>
-          <t>「Nnnn... Here we go！」</t>
+          <t>Nnnn... Here we go！</t>
         </is>
       </c>
       <c r="C984" t="n">
@@ -15547,7 +15548,7 @@
       </c>
       <c r="B985" s="1" t="inlineStr">
         <is>
-          <t>I flicked my wrist theatrically, but swung so the
+          <t>He flicked his wrist theatrically, but swung so the
 dice would fall straight down without scattering.</t>
         </is>
       </c>
@@ -15684,7 +15685,7 @@
       </c>
       <c r="B994" s="1" t="inlineStr">
         <is>
-          <t>I took the card Nono-chan happily handed me and
+          <t>He took the card Nono-chan happily handed him and
 turned it over with a wry smile.</t>
         </is>
       </c>
@@ -16200,7 +16201,7 @@
       </c>
       <c r="B1028" s="1" t="inlineStr">
         <is>
-          <t>Ah… ah, what should I do…！？</t>
+          <t>Ah… ah, what should I do…！？"</t>
         </is>
       </c>
       <c r="C1028" t="n">
@@ -16336,7 +16337,7 @@
       </c>
       <c r="B1037" s="1" t="inlineStr">
         <is>
-          <t>This sound... a helicopter！？</t>
+          <t>This sound... a helicopter！？"</t>
         </is>
       </c>
       <c r="C1037" t="n">
@@ -16352,7 +16353,7 @@
       <c r="B1038" s="1" t="inlineStr">
         <is>
           <t>Come to think of it, it's been a long time since we
-called for help—did they send a chopper！？</t>
+called for help—did they send a chopper！？"</t>
         </is>
       </c>
       <c r="C1038" t="n">
@@ -16460,7 +16461,7 @@
       <c r="B1045" s="1" t="inlineStr">
         <is>
           <t>You asked them to 'take care of it' and a helicopter
-showed up！？</t>
+showed up！？"</t>
         </is>
       </c>
       <c r="C1045" t="n">
@@ -16505,7 +16506,8 @@
       </c>
       <c r="B1048" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo-chan pulls out her phone and starts a call.</t>
+          <t>Rurichiyo-chan pulls out her phone and starts a
+call."</t>
         </is>
       </c>
       <c r="C1048" t="n">
@@ -16551,7 +16553,7 @@
       <c r="B1051" s="1" t="inlineStr">
         <is>
           <t>Rurichiyo-chan keeps calling out while tilting her
-head.</t>
+head."</t>
         </is>
       </c>
       <c r="C1051" t="n">
@@ -16567,7 +16569,7 @@
       <c r="B1052" s="1" t="inlineStr">
         <is>
           <t>Maybe they can't hear her over the helicopter
-noise...？</t>
+noise...？"</t>
         </is>
       </c>
       <c r="C1052" t="n">
@@ -16643,7 +16645,7 @@
       <c r="B1057" s="1" t="inlineStr">
         <is>
           <t>I took the phone from Rurichiyo-chan and held it up
-so I could hear better.</t>
+so I could hear better."</t>
         </is>
       </c>
       <c r="C1057" t="n">
@@ -16750,7 +16752,7 @@
       <c r="B1064" s="1" t="inlineStr">
         <is>
           <t>She started shouting over a loudspeaker, totally
-unrelated to the call！？</t>
+unrelated to the call！？"</t>
         </is>
       </c>
       <c r="C1064" t="n">
@@ -16797,7 +16799,7 @@
         <is>
           <t>...The person calling out from the helicopter's
 loudspeaker right now is my grandmother, Arisugawa
-Kikuchiyo—Rurichiyo-chan's great-grandmother.</t>
+Kikuchiyo—Rurichiyo-chan's great-grandmother."</t>
         </is>
       </c>
       <c r="C1067" t="n">
@@ -16813,7 +16815,7 @@
       <c r="B1068" s="1" t="inlineStr">
         <is>
           <t>Showing up out of nowhere by helicopter like that,
-she's as wild as ever...</t>
+he's as wild as ever...</t>
         </is>
       </c>
       <c r="C1068" t="n">
@@ -16860,7 +16862,7 @@
       <c r="B1071" s="1" t="inlineStr">
         <is>
           <t>Because the loudspeaker makes it a one-way
-conversation, she's repeatedly calling
+conversation, he's repeatedly calling
 Rurichiyo-chan's name.</t>
         </is>
       </c>
@@ -16893,7 +16895,7 @@
       <c r="B1073" s="1" t="inlineStr">
         <is>
           <t>Calling out 'Rurichiyo, Rurichiyo' at the drop of a
-hat is just how she usually is.</t>
+hat is just how he usually is.</t>
         </is>
       </c>
       <c r="C1073" t="n">
@@ -17443,8 +17445,8 @@
       </c>
       <c r="B1109" s="1" t="inlineStr">
         <is>
-          <t>「Also, I can have a normal conversation now, so you
-don't need to use the loudspeaker anymore.」</t>
+          <t>Also, I can have a normal conversation now, so you
+don't need to use the loudspeaker anymore.</t>
         </is>
       </c>
       <c r="C1109" t="n">
@@ -19162,7 +19164,7 @@
       <c r="B1221" s="1" t="inlineStr">
         <is>
           <t>If it's sleeping together, I have no problem with
-it... in fact, I'd welcome it.</t>
+it... in fact, I'd welcome it."</t>
         </is>
       </c>
       <c r="C1221" t="n">
@@ -20232,7 +20234,7 @@
       </c>
       <c r="B1291" s="1" t="inlineStr">
         <is>
-          <t>「Alright！ Then I'm gonna speed off—safely！」</t>
+          <t>Alright！ Then I'm gonna speed off—safely！</t>
         </is>
       </c>
       <c r="C1291" t="n">
@@ -21616,7 +21618,7 @@
       <c r="B1381" s="1" t="inlineStr">
         <is>
           <t>「Yes. I heard it only the other day from my
-great-grandmother.」</t>
+great-great-grandmother.」</t>
         </is>
       </c>
       <c r="C1381" t="n">
@@ -22442,7 +22444,7 @@
       </c>
       <c r="B1435" s="1" t="inlineStr">
         <is>
-          <t>「Shall I show you around, then？」</t>
+          <t>Shall I show you around, then？</t>
         </is>
       </c>
       <c r="C1435" t="n">
@@ -23132,7 +23134,7 @@
       </c>
       <c r="B1480" s="1" t="inlineStr">
         <is>
-          <t>「Wow！ Janitor-sensei, you can even be a cook！」</t>
+          <t>Wow！ Janitor-sensei, you can even be a cook！</t>
         </is>
       </c>
       <c r="C1480" t="n">
@@ -25348,8 +25350,8 @@
       </c>
       <c r="B1624" s="1" t="inlineStr">
         <is>
-          <t>「Eek...！ J-Janitor-sensei！ W-what... what should we
-do！?」</t>
+          <t>Eek...！ J-Janitor-sensei！ W-what... what should we
+do！?</t>
         </is>
       </c>
       <c r="C1624" t="n">
@@ -25396,7 +25398,7 @@
       </c>
       <c r="B1627" s="1" t="inlineStr">
         <is>
-          <t>「Honestly, you two, cut it out already.」</t>
+          <t>Honestly, you two, cut it out already.</t>
         </is>
       </c>
       <c r="C1627" t="n">
@@ -25533,7 +25535,7 @@
       </c>
       <c r="B1636" s="1" t="inlineStr">
         <is>
-          <t>「Both of you~~？ If you don't knock it off already...」</t>
+          <t>「Both of you~~？ If you don't knock it off already..."</t>
         </is>
       </c>
       <c r="C1636" t="n">
@@ -25548,7 +25550,7 @@
       </c>
       <c r="B1637" s="1" t="inlineStr">
         <is>
-          <t>"No-no！ I'm telling you！'</t>
+          <t>"No-no！ I'm telling you！」</t>
         </is>
       </c>
       <c r="C1637" t="n">
@@ -26334,7 +26336,7 @@
       </c>
       <c r="B1688" s="1" t="inlineStr">
         <is>
-          <t>「Let's give Janitor-sensei a gold star！」</t>
+          <t>Let's give Janitor-sensei a gold star！</t>
         </is>
       </c>
       <c r="C1688" t="n">
@@ -26801,7 +26803,7 @@
       </c>
       <c r="B1718" s="1" t="inlineStr">
         <is>
-          <t>「A bath really is the best...」</t>
+          <t>A bath really is the best...</t>
         </is>
       </c>
       <c r="C1718" t="n">
@@ -27585,7 +27587,7 @@
       </c>
       <c r="B1769" s="1" t="inlineStr">
         <is>
-          <t>「Ugh... uuu... uuuugh...！」</t>
+          <t>Ugh... uuu... uuuugh...！</t>
         </is>
       </c>
       <c r="C1769" t="n">
@@ -27648,7 +27650,7 @@
       </c>
       <c r="B1773" s="1" t="inlineStr">
         <is>
-          <t>「Ugh… um… I'm sorry」</t>
+          <t>Ugh… um… I」m sorry</t>
         </is>
       </c>
       <c r="C1773" t="n">
@@ -27710,8 +27712,8 @@
       </c>
       <c r="B1777" s="1" t="inlineStr">
         <is>
-          <t>「Excuse me, but may we join you in the place where
-you went in before us？」</t>
+          <t>Excuse me, but may we join you in the place where you
+went in before us？</t>
         </is>
       </c>
       <c r="C1777" t="n">
@@ -27945,7 +27947,7 @@
       </c>
       <c r="B1792" s="1" t="inlineStr">
         <is>
-          <t>「Rurichiyo-chan... you're an adult！？」</t>
+          <t>Rurichiyo-chan... you're an adult！？</t>
         </is>
       </c>
       <c r="C1792" t="n">
@@ -28144,8 +28146,7 @@
       </c>
       <c r="B1805" s="1" t="inlineStr">
         <is>
-          <t>「It sure is — the relationship doesn't change,
-right！」</t>
+          <t>It sure is — the relationship doesn't change, right！</t>
         </is>
       </c>
       <c r="C1805" t="n">
@@ -28315,8 +28316,8 @@
       </c>
       <c r="B1816" s="1" t="inlineStr">
         <is>
-          <t>「Phew... this water's just the right temperature,
-isn't it?」</t>
+          <t>Phew... this water's just the right temperature,
+isn't it?</t>
         </is>
       </c>
       <c r="C1816" t="n">
@@ -28532,7 +28533,7 @@
       </c>
       <c r="B1830" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo</t>
+          <t>Ruri</t>
         </is>
       </c>
       <c r="C1830" t="n">
@@ -28854,8 +28855,8 @@
       </c>
       <c r="B1851" s="1" t="inlineStr">
         <is>
-          <t>「Nnngh... I think it would be cruel to leave Oji-sama
-out...！」</t>
+          <t>Nnngh... I think it would be cruel to leave Oji-sama
+out...！</t>
         </is>
       </c>
       <c r="C1851" t="n">
@@ -30914,7 +30915,7 @@
       </c>
       <c r="B1985" s="1" t="inlineStr">
         <is>
-          <t>「All right then, Janitor-sensei, please！」</t>
+          <t>All right then, Janitor-sensei, please！</t>
         </is>
       </c>
       <c r="C1985" t="n">
@@ -31355,7 +31356,7 @@
       </c>
       <c r="B2014" s="1" t="inlineStr">
         <is>
-          <t>「So... kick...？」</t>
+          <t>So... kick...？</t>
         </is>
       </c>
       <c r="C2014" t="n">
@@ -32764,8 +32765,8 @@
       </c>
       <c r="B2106" s="1" t="inlineStr">
         <is>
-          <t>「Ah... amazing. Janitor-sensei looks like I'm really
-enjoying it...！」</t>
+          <t>Ah... amazing. Janitor-sensei looks like he's really
+enjoying it...！</t>
         </is>
       </c>
       <c r="C2106" t="n">
@@ -32871,7 +32872,7 @@
       </c>
       <c r="B2113" s="1" t="inlineStr">
         <is>
-          <t>「Hey, does it feel good？ Or does it hurt？」</t>
+          <t>Hey, does it feel good？ Or does it hurt？</t>
         </is>
       </c>
       <c r="C2113" t="n">
@@ -32962,8 +32963,8 @@
       </c>
       <c r="B2119" s="1" t="inlineStr">
         <is>
-          <t>「Rurichiyo-chan, I'm sure Janitor-sensei must be
-feeling good.」</t>
+          <t>Rurichiyo-chan, I'm sure Janitor-sensei must be
+feeling good.</t>
         </is>
       </c>
       <c r="C2119" t="n">
@@ -34720,7 +34721,7 @@
       </c>
       <c r="B2234" s="1" t="inlineStr">
         <is>
-          <t>Miruku</t>
+          <t>Miru</t>
         </is>
       </c>
       <c r="C2234" t="n">
@@ -34780,7 +34781,7 @@
       </c>
       <c r="B2238" s="1" t="inlineStr">
         <is>
-          <t>Miruku</t>
+          <t>Miru</t>
         </is>
       </c>
       <c r="C2238" t="n">
@@ -34872,7 +34873,7 @@
       </c>
       <c r="B2244" s="1" t="inlineStr">
         <is>
-          <t>Miruku</t>
+          <t>Miru</t>
         </is>
       </c>
       <c r="C2244" t="n">
@@ -34932,7 +34933,7 @@
       </c>
       <c r="B2248" s="1" t="inlineStr">
         <is>
-          <t>Miruku</t>
+          <t>Miru</t>
         </is>
       </c>
       <c r="C2248" t="n">
@@ -36983,8 +36984,8 @@
       </c>
       <c r="B2382" s="1" t="inlineStr">
         <is>
-          <t>「Haaah... It's amazing. It comes out this much,
-doesn't it？」</t>
+          <t>Haaah... It's amazing. It comes out this much,
+doesn't it？</t>
         </is>
       </c>
       <c r="C2382" t="n">
@@ -37078,7 +37079,7 @@
       </c>
       <c r="B2388" s="1" t="inlineStr">
         <is>
-          <t>「So this is... a guy's shasee, huh...」</t>
+          <t>So this is... a guy's shasee, huh...</t>
         </is>
       </c>
       <c r="C2388" t="n">
@@ -37309,7 +37310,7 @@
       </c>
       <c r="B2403" s="1" t="inlineStr">
         <is>
-          <t>Hajime</t>
+          <t>Hajime":""..."</t>
         </is>
       </c>
       <c r="C2403" t="n">
@@ -38181,7 +38182,7 @@
       </c>
       <c r="B2460" s="1" t="inlineStr">
         <is>
-          <t>「Ugh... it's still all sticky... what is this~？」</t>
+          <t>Ugh... it's still all sticky... what is this~？</t>
         </is>
       </c>
       <c r="C2460" t="n">
@@ -38443,7 +38444,7 @@
       </c>
       <c r="B2477" s="1" t="inlineStr">
         <is>
-          <t>「Ah！ Right, Rurichiyo hasn't done it yet, has she？」</t>
+          <t>Ah！ Right, Rurichiyo hasn't done it yet, has she？</t>
         </is>
       </c>
       <c r="C2477" t="n">
@@ -38473,7 +38474,7 @@
       </c>
       <c r="B2479" s="1" t="inlineStr">
         <is>
-          <t>「Heh！？ W-what is it？」</t>
+          <t>Heh！？ W-what is it？</t>
         </is>
       </c>
       <c r="C2479" t="n">
@@ -38675,8 +38676,8 @@
       </c>
       <c r="B2492" s="1" t="inlineStr">
         <is>
-          <t>「For starters, this kind of thing is really sexual,
-so it should only be done during sex！」</t>
+          <t>For starters, this kind of thing is really sexual, so
+it should only be done during sex！</t>
         </is>
       </c>
       <c r="C2492" t="n">
@@ -38829,8 +38830,8 @@
       </c>
       <c r="B2502" s="1" t="inlineStr">
         <is>
-          <t>「Y-yeah, that's right！ I really shouldn't be doing
-this, should I！」</t>
+          <t>Y-yeah, that's right！ I really shouldn't be doing
+this, should I！</t>
         </is>
       </c>
       <c r="C2502" t="n">
